--- a/data/数据收集 表3 蒙特卡洛模拟用.xlsx
+++ b/data/数据收集 表3 蒙特卡洛模拟用.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="87">
   <si>
     <t>源</t>
   </si>
@@ -203,42 +203,15 @@
     <t>XTE J1550-564</t>
   </si>
   <si>
-    <t>Kotrlová 2020</t>
-  </si>
-  <si>
-    <t>QPO</t>
-  </si>
-  <si>
-    <t>Šrámková 2015</t>
-  </si>
-  <si>
-    <t>Motta 2014</t>
-  </si>
-  <si>
-    <t>RPM</t>
-  </si>
-  <si>
-    <t>1998+2000</t>
-  </si>
-  <si>
     <t>1998-1999</t>
   </si>
   <si>
-    <t>Mukhopadhyay 2009</t>
-  </si>
-  <si>
-    <t>Kato 2006</t>
-  </si>
-  <si>
     <t>Davis 2006</t>
   </si>
   <si>
     <t>MAXI J1820+070</t>
   </si>
   <si>
-    <t>Fiori 2025</t>
-  </si>
-  <si>
     <t>Fan 2024</t>
   </si>
   <si>
@@ -258,9 +231,6 @@
   </si>
   <si>
     <t>Guan 2021</t>
-  </si>
-  <si>
-    <t>Bhargava 2021</t>
   </si>
   <si>
     <t>Bharali 2019</t>
@@ -1599,7 +1569,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R70"/>
+  <dimension ref="A1:R63"/>
   <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="29.5840707964602" style="3" customWidth="1"/>
@@ -2531,22 +2501,22 @@
         <v>57</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C35" s="16">
+        <v>0.49</v>
+      </c>
+      <c r="D35" s="16">
+        <v>0.2</v>
+      </c>
+      <c r="E35" s="16">
+        <v>0.13</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G35" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="C35" s="16">
-        <v>0.555</v>
-      </c>
-      <c r="D35" s="16">
-        <v>0.265</v>
-      </c>
-      <c r="E35" s="16">
-        <v>0.265</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="G35" s="20" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2554,22 +2524,22 @@
         <v>57</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C36" s="16">
-        <v>0.94</v>
+        <v>25</v>
+      </c>
+      <c r="C36" s="4">
+        <v>0.76</v>
       </c>
       <c r="D36" s="16">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="E36" s="16">
-        <v>0.05</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="G36" s="20" t="s">
-        <v>31</v>
+        <v>0.01</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G36" s="3">
+        <v>1998</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2577,157 +2547,157 @@
         <v>57</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C37" s="16">
-        <v>0.34</v>
+        <v>0.72</v>
       </c>
       <c r="D37" s="16">
         <v>0.01</v>
       </c>
       <c r="E37" s="16">
-        <v>0.01</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>62</v>
+        <v>0.15</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="38" spans="1:16">
       <c r="A38" s="22" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="C38" s="16">
-        <v>0.49</v>
-      </c>
-      <c r="D38" s="16">
-        <v>0.2</v>
-      </c>
-      <c r="E38" s="16">
-        <v>0.13</v>
+        <v>0.94</v>
+      </c>
+      <c r="D38" s="9">
+        <v>0.01</v>
+      </c>
+      <c r="E38" s="9">
+        <v>0.01</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>64</v>
+        <v>14</v>
+      </c>
+      <c r="G38" s="5">
+        <v>2018</v>
       </c>
     </row>
     <row r="39" spans="1:16">
       <c r="A39" s="22" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C39" s="16">
-        <v>0.725</v>
+        <v>-0.396</v>
       </c>
       <c r="D39" s="16">
-        <v>0.043</v>
+        <v>0.432</v>
       </c>
       <c r="E39" s="16">
-        <v>0.043</v>
-      </c>
-      <c r="F39" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="G39" s="20" t="s">
-        <v>31</v>
+        <v>0.661</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="40" spans="1:16">
       <c r="A40" s="22" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="C40" s="4">
-        <v>0.76</v>
+        <v>-0.141</v>
       </c>
       <c r="D40" s="16">
-        <v>0.01</v>
+        <v>0.564</v>
       </c>
       <c r="E40" s="16">
-        <v>0.01</v>
+        <v>0.492</v>
       </c>
       <c r="F40" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G40" s="3">
-        <v>1998</v>
+      <c r="G40" s="5" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="41" spans="1:16">
       <c r="A41" s="22" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C41" s="4">
-        <v>0.265</v>
-      </c>
-      <c r="D41" s="16">
-        <v>0.155</v>
-      </c>
-      <c r="E41" s="16">
-        <v>0.155</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="G41" s="20" t="s">
-        <v>31</v>
+        <v>0.77</v>
+      </c>
+      <c r="D41" s="9">
+        <v>0.21</v>
+      </c>
+      <c r="E41" s="9">
+        <v>0.21</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G41" s="5">
+        <v>2018</v>
       </c>
     </row>
     <row r="42" spans="1:16">
       <c r="A42" s="22" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C42" s="16">
-        <v>0.72</v>
+        <v>20</v>
+      </c>
+      <c r="C42" s="4">
+        <v>0.988</v>
       </c>
       <c r="D42" s="16">
-        <v>0.01</v>
+        <v>0.028</v>
       </c>
       <c r="E42" s="16">
-        <v>0.15</v>
+        <v>0.006</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>64</v>
+        <v>9</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="43" spans="1:16">
       <c r="A43" s="22" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C43" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>31</v>
+        <v>66</v>
+      </c>
+      <c r="C43" s="16">
+        <v>0.14</v>
+      </c>
+      <c r="D43" s="16">
+        <v>0.09</v>
       </c>
       <c r="E43" s="16">
-        <v>0</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>59</v>
+        <v>0.09</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="G43" s="5">
         <v>2018</v>
@@ -2735,19 +2705,19 @@
     </row>
     <row r="44" spans="1:16">
       <c r="A44" s="22" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C44" s="16">
-        <v>0.94</v>
-      </c>
-      <c r="D44" s="9">
-        <v>0.01</v>
-      </c>
-      <c r="E44" s="9">
-        <v>0.01</v>
+        <v>67</v>
+      </c>
+      <c r="C44" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="D44" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="E44" s="16">
+        <v>0.2</v>
       </c>
       <c r="F44" s="5" t="s">
         <v>14</v>
@@ -2758,206 +2728,206 @@
     </row>
     <row r="45" spans="1:16">
       <c r="A45" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="C45" s="16">
+        <v>0.998</v>
+      </c>
+      <c r="D45" s="27">
+        <v>0</v>
+      </c>
+      <c r="E45" s="27">
+        <v>0</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G45" s="5">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C46" s="4">
+        <v>0.79</v>
+      </c>
+      <c r="D46" s="27">
+        <v>0.13</v>
+      </c>
+      <c r="E46" s="27">
+        <v>0.13</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G46" s="3">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" s="4">
+        <v>0.977</v>
+      </c>
+      <c r="D47" s="4">
+        <v>0.015</v>
+      </c>
+      <c r="E47" s="4">
+        <v>0.017</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G47" s="3">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="A48" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C45" s="16">
-        <v>-0.396</v>
-      </c>
-      <c r="D45" s="16">
-        <v>0.432</v>
-      </c>
-      <c r="E45" s="16">
-        <v>0.661</v>
-      </c>
-      <c r="F45" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G45" s="5" t="s">
+      <c r="C48" s="16">
+        <v>0.41</v>
+      </c>
+      <c r="D48" s="16">
+        <v>0.03</v>
+      </c>
+      <c r="E48" s="16">
+        <v>0.03</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G48" s="3">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B49" s="3" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="46" spans="1:16">
-      <c r="A46" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="B46" s="3" t="s">
+      <c r="C49" s="4">
+        <v>0.82</v>
+      </c>
+      <c r="D49" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="E49" s="4">
+        <v>0.04</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G49" s="3">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C46" s="4">
-        <v>-0.141</v>
-      </c>
-      <c r="D46" s="16">
-        <v>0.564</v>
-      </c>
-      <c r="E46" s="16">
-        <v>0.492</v>
-      </c>
-      <c r="F46" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G46" s="5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16">
-      <c r="A47" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="B47" s="3" t="s">
+      <c r="C50" s="4">
+        <v>0.97</v>
+      </c>
+      <c r="D50" s="4">
+        <v>0</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G50" s="3">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C47" s="4">
-        <v>0.77</v>
-      </c>
-      <c r="D47" s="9">
-        <v>0.21</v>
-      </c>
-      <c r="E47" s="9">
-        <v>0.21</v>
-      </c>
-      <c r="F47" s="5" t="s">
+      <c r="C51" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="D51" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="E51" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="F51" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G47" s="5">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16">
-      <c r="A48" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C48" s="4">
-        <v>0.988</v>
-      </c>
-      <c r="D48" s="16">
-        <v>0.028</v>
-      </c>
-      <c r="E48" s="16">
-        <v>0.006</v>
-      </c>
-      <c r="F48" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G48" s="5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="B49" s="3" t="s">
+      <c r="G51" s="3">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C49" s="16">
-        <v>0.14</v>
-      </c>
-      <c r="D49" s="16">
-        <v>0.09</v>
-      </c>
-      <c r="E49" s="16">
-        <v>0.09</v>
-      </c>
-      <c r="F49" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G49" s="5">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C50" s="4">
-        <v>0.2</v>
-      </c>
-      <c r="D50" s="16">
-        <v>0.3</v>
-      </c>
-      <c r="E50" s="16">
-        <v>0.2</v>
-      </c>
-      <c r="F50" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G50" s="5">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C51" s="4">
-        <v>0.799</v>
-      </c>
-      <c r="D51" s="16">
-        <v>0.015</v>
-      </c>
-      <c r="E51" s="16">
-        <v>0.016</v>
-      </c>
-      <c r="F51" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="G51" s="5">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C52" s="16">
-        <v>0.998</v>
-      </c>
-      <c r="D52" s="27">
-        <v>0</v>
-      </c>
-      <c r="E52" s="27">
-        <v>0</v>
+      <c r="C52" s="4">
+        <v>0.78</v>
+      </c>
+      <c r="D52" s="4">
+        <v>0.04</v>
+      </c>
+      <c r="E52" s="4">
+        <v>0.04</v>
       </c>
       <c r="F52" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G52" s="5">
-        <v>2018</v>
+      <c r="G52" s="3">
+        <v>2019</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C53" s="4">
-        <v>0.79</v>
+        <v>77</v>
+      </c>
+      <c r="C53" s="27">
+        <v>0.2</v>
       </c>
       <c r="D53" s="27">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="E53" s="27">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="G53" s="3">
         <v>2019</v>
@@ -2965,22 +2935,22 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C54" s="4">
-        <v>0.977</v>
-      </c>
-      <c r="D54" s="4">
-        <v>0.015</v>
-      </c>
-      <c r="E54" s="4">
-        <v>0.017</v>
+        <v>78</v>
+      </c>
+      <c r="C54" s="16">
+        <v>0.86</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E54" s="16">
+        <v>0</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G54" s="3">
         <v>2019</v>
@@ -2988,22 +2958,22 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C55" s="16">
-        <v>0.41</v>
-      </c>
-      <c r="D55" s="16">
-        <v>0.03</v>
-      </c>
-      <c r="E55" s="16">
-        <v>0.03</v>
+      <c r="C55" s="4">
+        <v>0.72</v>
+      </c>
+      <c r="D55" s="4">
+        <v>0</v>
+      </c>
+      <c r="E55" s="9" t="s">
+        <v>31</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G55" s="3">
         <v>2019</v>
@@ -3011,19 +2981,19 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="C56" s="4">
-        <v>0.82</v>
+        <v>0.97</v>
       </c>
       <c r="D56" s="4">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E56" s="4">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="F56" s="5" t="s">
         <v>9</v>
@@ -3034,22 +3004,22 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C57" s="4">
-        <v>0.97</v>
-      </c>
-      <c r="D57" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E57" s="4">
         <v>0</v>
       </c>
-      <c r="E57" s="9" t="s">
-        <v>31</v>
-      </c>
       <c r="F57" s="5" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="G57" s="3">
         <v>2019</v>
@@ -3057,300 +3027,139 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C58" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="D58" s="4">
-        <v>0.02</v>
-      </c>
-      <c r="E58" s="4">
-        <v>0.02</v>
+        <v>82</v>
+      </c>
+      <c r="C58" s="16">
+        <v>0.655</v>
+      </c>
+      <c r="D58" s="27">
+        <v>0.155</v>
+      </c>
+      <c r="E58" s="27">
+        <v>0.155</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G58" s="3">
-        <v>2019</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="C59" s="4">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="D59" s="4">
-        <v>0.04</v>
+        <v>0.26</v>
       </c>
       <c r="E59" s="4">
-        <v>0.04</v>
+        <v>0.17</v>
       </c>
       <c r="F59" s="5" t="s">
         <v>9</v>
       </c>
       <c r="G59" s="3">
-        <v>2019</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C60" s="27">
-        <v>0.2</v>
+        <v>83</v>
+      </c>
+      <c r="C60" s="16">
+        <v>0.7</v>
       </c>
       <c r="D60" s="27">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="E60" s="27">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="F60" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G60" s="3">
-        <v>2019</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C61" s="16">
-        <v>0.86</v>
-      </c>
-      <c r="D61" s="9" t="s">
-        <v>31</v>
+        <v>0.94</v>
+      </c>
+      <c r="D61" s="16">
+        <v>0.03</v>
       </c>
       <c r="E61" s="16">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G61" s="3">
-        <v>2019</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B62" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B62" s="3" t="s">
-        <v>89</v>
-      </c>
       <c r="C62" s="4">
-        <v>0.72</v>
-      </c>
-      <c r="D62" s="4">
-        <v>0</v>
-      </c>
-      <c r="E62" s="9" t="s">
-        <v>31</v>
+        <v>0.49</v>
+      </c>
+      <c r="D62" s="16">
+        <v>0.22</v>
+      </c>
+      <c r="E62" s="16">
+        <v>0.07</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G62" s="3">
-        <v>2019</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C63" s="4">
-        <v>0.97</v>
-      </c>
-      <c r="D63" s="4">
-        <v>0.02</v>
-      </c>
-      <c r="E63" s="4">
-        <v>0.02</v>
+        <v>82</v>
+      </c>
+      <c r="C63" s="16">
+        <v>0.665</v>
+      </c>
+      <c r="D63" s="27">
+        <v>0.035</v>
+      </c>
+      <c r="E63" s="27">
+        <v>0.035</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G63" s="3">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
-      <c r="A64" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C64" s="4">
-        <v>0.25</v>
-      </c>
-      <c r="D64" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="E64" s="4">
-        <v>0</v>
-      </c>
-      <c r="F64" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G64" s="3">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
-      <c r="A65" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C65" s="16">
-        <v>0.655</v>
-      </c>
-      <c r="D65" s="27">
-        <v>0.155</v>
-      </c>
-      <c r="E65" s="27">
-        <v>0.155</v>
-      </c>
-      <c r="F65" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G65" s="3">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7">
-      <c r="A66" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C66" s="4">
-        <v>0.84</v>
-      </c>
-      <c r="D66" s="4">
-        <v>0.26</v>
-      </c>
-      <c r="E66" s="4">
-        <v>0.17</v>
-      </c>
-      <c r="F66" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G66" s="3">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7">
-      <c r="A67" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C67" s="16">
-        <v>0.7</v>
-      </c>
-      <c r="D67" s="27">
-        <v>0.17</v>
-      </c>
-      <c r="E67" s="27">
-        <v>0.17</v>
-      </c>
-      <c r="F67" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G67" s="3">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7">
-      <c r="A68" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C68" s="16">
-        <v>0.94</v>
-      </c>
-      <c r="D68" s="16">
-        <v>0.03</v>
-      </c>
-      <c r="E68" s="16">
-        <v>0.06</v>
-      </c>
-      <c r="F68" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G68" s="3">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7">
-      <c r="A69" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C69" s="4">
-        <v>0.49</v>
-      </c>
-      <c r="D69" s="16">
-        <v>0.22</v>
-      </c>
-      <c r="E69" s="16">
-        <v>0.07</v>
-      </c>
-      <c r="F69" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G69" s="3">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7">
-      <c r="A70" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C70" s="16">
-        <v>0.665</v>
-      </c>
-      <c r="D70" s="27">
-        <v>0.035</v>
-      </c>
-      <c r="E70" s="27">
-        <v>0.035</v>
-      </c>
-      <c r="F70" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G70" s="3">
         <v>2025</v>
       </c>
     </row>

--- a/data/数据收集 表3 蒙特卡洛模拟用.xlsx
+++ b/data/数据收集 表3 蒙特卡洛模拟用.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="88">
   <si>
     <t>源</t>
   </si>
@@ -42,6 +42,9 @@
   </si>
   <si>
     <t>自旋值i +</t>
+  </si>
+  <si>
+    <t>自旋值i 置信度(σ)</t>
   </si>
   <si>
     <t>拟合模型</t>
@@ -975,6 +978,9 @@
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1001,9 +1007,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1569,7 +1572,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R63"/>
+  <dimension ref="A1:S63"/>
   <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="29.5840707964602" style="3" customWidth="1"/>
@@ -1577,576 +1580,643 @@
     <col min="3" max="3" width="8.96460176991151" style="4" customWidth="1"/>
     <col min="4" max="5" width="11.2212389380531" style="4" customWidth="1"/>
     <col min="6" max="6" width="38.5132743362832" style="5" customWidth="1"/>
-    <col min="7" max="7" width="24.2920353982301" style="3" customWidth="1"/>
+    <col min="7" max="7" width="38.5132743362832" style="6" customWidth="1"/>
+    <col min="8" max="8" width="24.2920353982301" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:7">
-      <c r="A2" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:8">
+      <c r="A2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="9">
+      <c r="B2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="10">
         <v>0.817</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="10">
         <v>0.014</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="10">
         <v>0.014</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="5">
+      <c r="F2" s="5">
+        <v>1.645</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="6">
         <v>2020</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:7">
-      <c r="A3" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="5" t="s">
+    <row r="3" s="1" customFormat="1" spans="1:8">
+      <c r="A3" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="10">
+        <v>0.99</v>
+      </c>
+      <c r="D3" s="10">
+        <v>0.003</v>
+      </c>
+      <c r="E3" s="10">
+        <v>0.003</v>
+      </c>
+      <c r="F3" s="5">
+        <v>1</v>
+      </c>
+      <c r="G3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="9">
-        <v>0.99</v>
-      </c>
-      <c r="D3" s="9">
-        <v>0.003</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.003</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="5">
+      <c r="H3" s="6">
         <v>2013</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:7">
-      <c r="A4" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="10">
+    <row r="4" s="1" customFormat="1" spans="1:8">
+      <c r="A4" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="11">
         <v>0.85</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="10">
         <v>0.07</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="10">
         <v>0.07</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:7">
-      <c r="A5" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="F4" s="5">
+        <v>1.645</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="10">
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:8">
+      <c r="A5" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="11">
         <v>0.92</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="10">
         <v>0.04</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="10">
         <v>0.04</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="5">
+      <c r="F5" s="5">
+        <v>3</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="6">
         <v>2016</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:7">
-      <c r="A6" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="5" t="s">
+    <row r="6" s="1" customFormat="1" spans="1:8">
+      <c r="A6" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="11">
+        <v>0.985</v>
+      </c>
+      <c r="D6" s="10">
+        <v>0.014</v>
+      </c>
+      <c r="E6" s="10">
+        <v>0.005</v>
+      </c>
+      <c r="F6" s="5">
+        <v>1</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="6">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:8">
+      <c r="A7" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="10">
+        <v>0.902</v>
+      </c>
+      <c r="D7" s="10">
+        <v>0.053</v>
+      </c>
+      <c r="E7" s="10">
+        <v>0.054</v>
+      </c>
+      <c r="F7" s="5">
+        <v>1.645</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="6">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:8">
+      <c r="A8" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="10">
+        <v>0.959</v>
+      </c>
+      <c r="D8" s="11">
+        <v>0.039</v>
+      </c>
+      <c r="E8" s="11">
+        <v>0.031</v>
+      </c>
+      <c r="F8" s="5">
+        <v>1</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="6">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="9" s="2" customFormat="1" spans="1:8">
+      <c r="A9" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="11">
+        <v>0.65</v>
+      </c>
+      <c r="D9" s="11">
+        <v>0.24</v>
+      </c>
+      <c r="E9" s="11">
+        <v>0.14</v>
+      </c>
+      <c r="F9" s="5">
+        <v>1</v>
+      </c>
+      <c r="G9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="10">
-        <v>0.985</v>
-      </c>
-      <c r="D6" s="9">
-        <v>0.014</v>
-      </c>
-      <c r="E6" s="9">
-        <v>0.005</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" s="5">
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:7">
-      <c r="A7" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="5" t="s">
+      <c r="H9" s="6">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" spans="1:8">
+      <c r="A10" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="9">
-        <v>0.902</v>
-      </c>
-      <c r="D7" s="9">
-        <v>0.053</v>
-      </c>
-      <c r="E7" s="9">
-        <v>0.054</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" s="5">
+      <c r="B10" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="D10" s="11">
+        <v>0.02</v>
+      </c>
+      <c r="E10" s="11">
+        <v>0.01</v>
+      </c>
+      <c r="F10" s="5">
+        <v>1</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="6">
         <v>2021</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" spans="1:7">
-      <c r="A8" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="9">
-        <v>0.959</v>
-      </c>
-      <c r="D8" s="10">
-        <v>0.039</v>
-      </c>
-      <c r="E8" s="10">
-        <v>0.031</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" s="5">
-        <v>2017</v>
-      </c>
-    </row>
-    <row r="9" s="2" customFormat="1" spans="1:7">
-      <c r="A9" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="10">
-        <v>0.65</v>
-      </c>
-      <c r="D9" s="10">
-        <v>0.24</v>
-      </c>
-      <c r="E9" s="10">
-        <v>0.14</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="5">
+    <row r="11" s="1" customFormat="1" spans="1:8">
+      <c r="A11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="10">
+        <v>0.46</v>
+      </c>
+      <c r="D11" s="11">
+        <v>0.12</v>
+      </c>
+      <c r="E11" s="11">
+        <v>0.12</v>
+      </c>
+      <c r="F11" s="5">
+        <v>1</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="6">
         <v>2021</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" spans="1:7">
-      <c r="A10" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="10">
-        <v>0.98</v>
-      </c>
-      <c r="D10" s="10">
-        <v>0.02</v>
-      </c>
-      <c r="E10" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10" s="5">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:7">
-      <c r="A11" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="9">
-        <v>0.46</v>
-      </c>
-      <c r="D11" s="10">
-        <v>0.12</v>
-      </c>
-      <c r="E11" s="10">
-        <v>0.12</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" s="5">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:7">
-      <c r="A12" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="9">
+    <row r="12" s="1" customFormat="1" spans="1:8">
+      <c r="A12" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="10">
         <v>0.67</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="11">
         <v>0.08</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="11">
         <v>0.15</v>
       </c>
-      <c r="F12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12" s="5">
+      <c r="F12" s="5">
+        <v>1.645</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" s="6">
         <v>2002</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" spans="1:7">
-      <c r="A13" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="9">
+    <row r="13" s="1" customFormat="1" spans="1:8">
+      <c r="A13" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="10">
         <v>0.43</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="11">
         <v>0.31</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="11">
         <v>0.22</v>
       </c>
-      <c r="F13" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G13" s="5">
+      <c r="F13" s="5">
+        <v>1.645</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13" s="6">
         <v>2002</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" spans="1:7">
-      <c r="A14" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="5" t="s">
+    <row r="14" s="1" customFormat="1" spans="1:8">
+      <c r="A14" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="D14" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="E14" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="F14" s="5">
+        <v>1</v>
+      </c>
+      <c r="G14" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="9">
-        <v>0.3</v>
-      </c>
-      <c r="D14" s="10">
-        <v>0.1</v>
-      </c>
-      <c r="E14" s="10">
-        <v>0.1</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G14" s="5">
+      <c r="H14" s="6">
         <v>2002</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" spans="1:7">
-      <c r="A15" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="9">
+    <row r="15" s="1" customFormat="1" spans="1:8">
+      <c r="A15" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="10">
         <v>0.8</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="10">
         <v>0.05</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="10">
         <v>0.05</v>
       </c>
-      <c r="F15" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15" s="5">
+      <c r="F15" s="5">
+        <v>1</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="6">
         <v>2002</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" spans="1:7">
-      <c r="A16" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="5" t="s">
+    <row r="16" s="1" customFormat="1" spans="1:8">
+      <c r="A16" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="9">
+      <c r="B16" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="10">
         <v>0.77</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="10">
         <v>0.22</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="10">
         <v>0.22</v>
       </c>
-      <c r="F16" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="1:18">
-      <c r="A17" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="5" t="s">
+      <c r="F16" s="5">
+        <v>1.645</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="14">
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:19">
+      <c r="A17" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="5">
         <v>0.976</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="11">
         <v>0</v>
       </c>
-      <c r="E17" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G17" s="5">
+      <c r="E17" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" s="5">
+        <v>1.645</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" s="6">
         <v>2020</v>
       </c>
     </row>
-    <row r="18" customFormat="1" spans="1:18">
+    <row r="18" customFormat="1" spans="1:19">
       <c r="A18" s="15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C18" s="16">
         <v>0.71</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="10">
         <v>0.04</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="10">
         <v>0.05</v>
       </c>
-      <c r="F18" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G18" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="18"/>
+      <c r="F18" s="5">
+        <v>1.645</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H18" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
       <c r="M18" s="18"/>
       <c r="N18" s="18"/>
       <c r="O18" s="18"/>
-      <c r="P18" s="19"/>
+      <c r="P18" s="18"/>
       <c r="Q18" s="19"/>
       <c r="R18" s="19"/>
-    </row>
-    <row r="19" customFormat="1" spans="1:18">
+      <c r="S18" s="19"/>
+    </row>
+    <row r="19" customFormat="1" spans="1:19">
       <c r="A19" s="15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C19" s="16">
         <v>0.8</v>
       </c>
-      <c r="D19" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" s="9">
+      <c r="D19" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" s="10">
         <v>0</v>
       </c>
-      <c r="F19" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G19" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="12"/>
-      <c r="L19" s="18"/>
+      <c r="F19" s="5">
+        <v>1.645</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="13"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="13"/>
       <c r="M19" s="18"/>
       <c r="N19" s="18"/>
       <c r="O19" s="18"/>
-      <c r="P19" s="19"/>
+      <c r="P19" s="18"/>
       <c r="Q19" s="19"/>
       <c r="R19" s="19"/>
-    </row>
-    <row r="20" customFormat="1" spans="1:18">
+      <c r="S19" s="19"/>
+    </row>
+    <row r="20" customFormat="1" spans="1:19">
       <c r="A20" s="15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C20" s="16">
         <v>0.95</v>
       </c>
-      <c r="D20" s="9">
+      <c r="D20" s="10">
         <v>0.05</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="10">
         <v>0.03</v>
       </c>
-      <c r="F20" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G20" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="12"/>
-      <c r="K20" s="12"/>
-      <c r="L20" s="18"/>
+      <c r="F20" s="5">
+        <v>1.645</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+      <c r="L20" s="13"/>
       <c r="M20" s="18"/>
       <c r="N20" s="18"/>
       <c r="O20" s="18"/>
-      <c r="P20" s="19"/>
+      <c r="P20" s="18"/>
       <c r="Q20" s="19"/>
       <c r="R20" s="19"/>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="1:18">
+      <c r="S20" s="19"/>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:19">
       <c r="A21" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="10">
+        <v>0.97</v>
+      </c>
+      <c r="D21" s="10">
+        <v>0</v>
+      </c>
+      <c r="E21" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C21" s="9">
-        <v>0.97</v>
-      </c>
-      <c r="D21" s="9">
-        <v>0</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G21" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
-      <c r="K21" s="12"/>
-      <c r="L21" s="18"/>
+      <c r="F21" s="5">
+        <v>1.645</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="I21" s="13"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13"/>
+      <c r="L21" s="13"/>
       <c r="M21" s="18"/>
       <c r="N21" s="18"/>
       <c r="O21" s="18"/>
-      <c r="P21" s="21"/>
+      <c r="P21" s="18"/>
       <c r="Q21" s="21"/>
       <c r="R21" s="21"/>
-    </row>
-    <row r="22" customFormat="1" spans="1:18">
+      <c r="S21" s="21"/>
+    </row>
+    <row r="22" customFormat="1" spans="1:19">
       <c r="A22" s="15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C22" s="16">
         <v>0.4</v>
       </c>
-      <c r="D22" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="E22" s="9">
+      <c r="D22" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="10">
         <v>0</v>
       </c>
-      <c r="F22" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G22" s="22">
+      <c r="F22" s="5">
+        <v>1</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H22" s="22">
         <v>2007</v>
       </c>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="12"/>
-      <c r="K22" s="12"/>
-      <c r="L22" s="18"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="13"/>
+      <c r="L22" s="13"/>
       <c r="M22" s="18"/>
       <c r="N22" s="18"/>
       <c r="O22" s="18"/>
-      <c r="P22" s="19"/>
+      <c r="P22" s="18"/>
       <c r="Q22" s="19"/>
       <c r="R22" s="19"/>
-    </row>
-    <row r="23" customFormat="1" spans="1:18">
+      <c r="S22" s="19"/>
+    </row>
+    <row r="23" customFormat="1" spans="1:19">
       <c r="A23" s="15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C23" s="16">
         <v>0.89</v>
@@ -2157,64 +2227,70 @@
       <c r="E23" s="16">
         <v>0.04</v>
       </c>
-      <c r="F23" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G23" s="22">
+      <c r="F23" s="5">
+        <v>1</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H23" s="22">
         <v>2007</v>
       </c>
-      <c r="H23" s="23"/>
       <c r="I23" s="23"/>
-      <c r="J23" s="12"/>
-      <c r="K23" s="12"/>
-      <c r="L23" s="12"/>
-      <c r="M23" s="8"/>
-      <c r="N23" s="12"/>
-      <c r="O23" s="24"/>
-      <c r="P23" s="19"/>
+      <c r="J23" s="23"/>
+      <c r="K23" s="13"/>
+      <c r="L23" s="13"/>
+      <c r="M23" s="13"/>
+      <c r="N23" s="9"/>
+      <c r="O23" s="13"/>
+      <c r="P23" s="24"/>
       <c r="Q23" s="19"/>
       <c r="R23" s="19"/>
-    </row>
-    <row r="24" customFormat="1" spans="1:18">
+      <c r="S23" s="19"/>
+    </row>
+    <row r="24" customFormat="1" spans="1:19">
       <c r="A24" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="C24" s="16">
         <v>0.85</v>
       </c>
-      <c r="D24" s="10">
+      <c r="D24" s="11">
         <v>0.05</v>
       </c>
-      <c r="E24" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G24" s="12">
+      <c r="E24" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" s="5">
+        <v>1</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H24" s="13">
         <v>2002</v>
       </c>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12"/>
-      <c r="J24" s="12"/>
-      <c r="K24" s="12"/>
-      <c r="L24" s="12"/>
-      <c r="M24" s="8"/>
-      <c r="N24" s="12"/>
-      <c r="O24" s="24"/>
-      <c r="P24" s="19"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="13"/>
+      <c r="M24" s="13"/>
+      <c r="N24" s="9"/>
+      <c r="O24" s="13"/>
+      <c r="P24" s="24"/>
       <c r="Q24" s="19"/>
       <c r="R24" s="19"/>
-    </row>
-    <row r="25" spans="1:18">
+      <c r="S24" s="19"/>
+    </row>
+    <row r="25" spans="1:19">
       <c r="A25" s="22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C25" s="16">
         <v>0.98</v>
@@ -2225,22 +2301,25 @@
       <c r="E25" s="16">
         <v>0.01</v>
       </c>
-      <c r="F25" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G25" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="H25" s="25"/>
+      <c r="F25" s="5">
+        <v>1</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H25" s="20" t="s">
+        <v>32</v>
+      </c>
       <c r="I25" s="25"/>
       <c r="J25" s="25"/>
-    </row>
-    <row r="26" spans="1:18">
+      <c r="K25" s="25"/>
+    </row>
+    <row r="26" spans="1:19">
       <c r="A26" s="22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C26" s="16">
         <v>0.2</v>
@@ -2251,22 +2330,25 @@
       <c r="E26" s="16">
         <v>0.3</v>
       </c>
-      <c r="F26" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G26" s="25">
+      <c r="F26" s="5">
+        <v>1</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H26" s="25">
         <v>2003</v>
       </c>
-      <c r="H26" s="25"/>
       <c r="I26" s="25"/>
       <c r="J26" s="25"/>
-    </row>
-    <row r="27" spans="1:18">
+      <c r="K26" s="25"/>
+    </row>
+    <row r="27" spans="1:19">
       <c r="A27" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C27" s="4">
         <v>0.88</v>
@@ -2277,71 +2359,80 @@
       <c r="E27" s="16">
         <v>0.01</v>
       </c>
-      <c r="F27" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G27" s="25">
+      <c r="F27" s="5">
+        <v>1.645</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H27" s="25">
         <v>2023</v>
       </c>
-      <c r="H27" s="25"/>
       <c r="I27" s="25"/>
       <c r="J27" s="25"/>
-    </row>
-    <row r="28" s="1" customFormat="1" spans="1:18">
+      <c r="K27" s="25"/>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="1:19">
       <c r="A28" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C28" s="9">
+        <v>46</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" s="10">
         <v>0.85</v>
       </c>
-      <c r="D28" s="9">
+      <c r="D28" s="10">
         <v>0.03</v>
       </c>
-      <c r="E28" s="9">
+      <c r="E28" s="10">
         <v>0.03</v>
       </c>
-      <c r="F28" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G28" s="25">
+      <c r="F28" s="5">
+        <v>1.645</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H28" s="25">
         <v>2023</v>
       </c>
-      <c r="H28" s="25"/>
       <c r="I28" s="25"/>
       <c r="J28" s="25"/>
-    </row>
-    <row r="29" s="1" customFormat="1" spans="1:18">
+      <c r="K28" s="25"/>
+    </row>
+    <row r="29" s="1" customFormat="1" spans="1:19">
       <c r="A29" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C29" s="9">
+        <v>46</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29" s="10">
         <v>0.8</v>
       </c>
-      <c r="D29" s="10">
+      <c r="D29" s="11">
         <v>0</v>
       </c>
-      <c r="E29" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G29" s="25">
+      <c r="E29" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F29" s="5">
+        <v>1.645</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H29" s="25">
         <v>2023</v>
       </c>
     </row>
-    <row r="30" spans="1:18">
+    <row r="30" spans="1:19">
       <c r="A30" s="22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C30" s="16">
         <v>0.863</v>
@@ -2352,13 +2443,15 @@
       <c r="E30" s="16">
         <v>0.014</v>
       </c>
-      <c r="F30" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G30" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="H30" s="25"/>
+      <c r="F30" s="5">
+        <v>2.576</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" s="25" t="s">
+        <v>52</v>
+      </c>
       <c r="I30" s="25"/>
       <c r="J30" s="25"/>
       <c r="K30" s="25"/>
@@ -2367,13 +2460,14 @@
       <c r="N30" s="25"/>
       <c r="O30" s="25"/>
       <c r="P30" s="25"/>
-    </row>
-    <row r="31" spans="1:18">
+      <c r="Q30" s="25"/>
+    </row>
+    <row r="31" spans="1:19">
       <c r="A31" s="22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C31" s="16">
         <v>0.98</v>
@@ -2384,13 +2478,15 @@
       <c r="E31" s="16">
         <v>0.01</v>
       </c>
-      <c r="F31" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G31" s="25">
+      <c r="F31" s="5">
+        <v>999999</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H31" s="25">
         <v>2012</v>
       </c>
-      <c r="H31" s="25"/>
       <c r="I31" s="25"/>
       <c r="J31" s="25"/>
       <c r="K31" s="25"/>
@@ -2399,13 +2495,14 @@
       <c r="N31" s="25"/>
       <c r="O31" s="25"/>
       <c r="P31" s="25"/>
-    </row>
-    <row r="32" spans="1:18">
+      <c r="Q31" s="25"/>
+    </row>
+    <row r="32" spans="1:19">
       <c r="A32" s="22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B32" s="25" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C32" s="26">
         <v>0.98</v>
@@ -2416,13 +2513,15 @@
       <c r="E32" s="16">
         <v>0.01</v>
       </c>
-      <c r="F32" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G32" s="25">
+      <c r="F32" s="5">
+        <v>1</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H32" s="25">
         <v>2007</v>
       </c>
-      <c r="H32" s="25"/>
       <c r="I32" s="25"/>
       <c r="J32" s="25"/>
       <c r="K32" s="25"/>
@@ -2431,13 +2530,14 @@
       <c r="N32" s="25"/>
       <c r="O32" s="25"/>
       <c r="P32" s="25"/>
-    </row>
-    <row r="33" spans="1:16">
+      <c r="Q32" s="25"/>
+    </row>
+    <row r="33" spans="1:17">
       <c r="A33" s="22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C33" s="16">
         <v>0.98</v>
@@ -2445,16 +2545,18 @@
       <c r="D33" s="16">
         <v>0</v>
       </c>
-      <c r="E33" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G33" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="H33" s="25"/>
+      <c r="E33" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F33" s="5">
+        <v>2.576</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H33" s="25" t="s">
+        <v>52</v>
+      </c>
       <c r="I33" s="25"/>
       <c r="J33" s="25"/>
       <c r="K33" s="25"/>
@@ -2463,13 +2565,14 @@
       <c r="N33" s="25"/>
       <c r="O33" s="25"/>
       <c r="P33" s="25"/>
-    </row>
-    <row r="34" spans="1:16">
+      <c r="Q33" s="25"/>
+    </row>
+    <row r="34" spans="1:17">
       <c r="A34" s="22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C34" s="16">
         <v>0.72</v>
@@ -2480,13 +2583,15 @@
       <c r="E34" s="16">
         <v>0.009</v>
       </c>
-      <c r="F34" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G34" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="H34" s="25"/>
+      <c r="F34" s="5">
+        <v>1.645</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H34" s="25" t="s">
+        <v>57</v>
+      </c>
       <c r="I34" s="25"/>
       <c r="J34" s="25"/>
       <c r="K34" s="25"/>
@@ -2495,13 +2600,14 @@
       <c r="N34" s="25"/>
       <c r="O34" s="25"/>
       <c r="P34" s="25"/>
-    </row>
-    <row r="35" spans="1:16">
+      <c r="Q34" s="25"/>
+    </row>
+    <row r="35" spans="1:17">
       <c r="A35" s="22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C35" s="16">
         <v>0.49</v>
@@ -2512,19 +2618,22 @@
       <c r="E35" s="16">
         <v>0.13</v>
       </c>
-      <c r="F35" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G35" s="3" t="s">
+      <c r="F35" s="5">
+        <v>1.645</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17">
+      <c r="A36" s="22" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="36" spans="1:16">
-      <c r="A36" s="22" t="s">
-        <v>57</v>
-      </c>
       <c r="B36" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C36" s="4">
         <v>0.76</v>
@@ -2535,19 +2644,22 @@
       <c r="E36" s="16">
         <v>0.01</v>
       </c>
-      <c r="F36" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G36" s="3">
+      <c r="F36" s="5">
+        <v>1</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H36" s="3">
         <v>1998</v>
       </c>
     </row>
-    <row r="37" spans="1:16">
+    <row r="37" spans="1:17">
       <c r="A37" s="22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C37" s="16">
         <v>0.72</v>
@@ -2558,42 +2670,48 @@
       <c r="E37" s="16">
         <v>0.15</v>
       </c>
-      <c r="F37" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16">
+      <c r="F37" s="5">
+        <v>1.645</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17">
       <c r="A38" s="22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C38" s="16">
         <v>0.94</v>
       </c>
-      <c r="D38" s="9">
+      <c r="D38" s="10">
         <v>0.01</v>
       </c>
-      <c r="E38" s="9">
+      <c r="E38" s="10">
         <v>0.01</v>
       </c>
-      <c r="F38" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G38" s="5">
+      <c r="F38" s="5">
+        <v>1.645</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H38" s="6">
         <v>2018</v>
       </c>
     </row>
-    <row r="39" spans="1:16">
+    <row r="39" spans="1:17">
       <c r="A39" s="22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C39" s="16">
         <v>-0.396</v>
@@ -2604,19 +2722,22 @@
       <c r="E39" s="16">
         <v>0.661</v>
       </c>
-      <c r="F39" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16">
+      <c r="F39" s="5">
+        <v>1</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17">
       <c r="A40" s="22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C40" s="4">
         <v>-0.141</v>
@@ -2627,42 +2748,48 @@
       <c r="E40" s="16">
         <v>0.492</v>
       </c>
-      <c r="F40" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G40" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16">
+      <c r="F40" s="5">
+        <v>1</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17">
       <c r="A41" s="22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C41" s="4">
         <v>0.77</v>
       </c>
-      <c r="D41" s="9">
+      <c r="D41" s="10">
         <v>0.21</v>
       </c>
-      <c r="E41" s="9">
+      <c r="E41" s="10">
         <v>0.21</v>
       </c>
-      <c r="F41" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G41" s="5">
+      <c r="F41" s="5">
+        <v>1.645</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H41" s="6">
         <v>2018</v>
       </c>
     </row>
-    <row r="42" spans="1:16">
+    <row r="42" spans="1:17">
       <c r="A42" s="22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C42" s="4">
         <v>0.988</v>
@@ -2673,19 +2800,22 @@
       <c r="E42" s="16">
         <v>0.006</v>
       </c>
-      <c r="F42" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16">
+      <c r="F42" s="5">
+        <v>1</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17">
       <c r="A43" s="22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C43" s="16">
         <v>0.14</v>
@@ -2696,19 +2826,22 @@
       <c r="E43" s="16">
         <v>0.09</v>
       </c>
-      <c r="F43" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G43" s="5">
+      <c r="F43" s="5">
+        <v>1</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H43" s="6">
         <v>2018</v>
       </c>
     </row>
-    <row r="44" spans="1:16">
+    <row r="44" spans="1:17">
       <c r="A44" s="22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C44" s="4">
         <v>0.2</v>
@@ -2719,19 +2852,22 @@
       <c r="E44" s="16">
         <v>0.2</v>
       </c>
-      <c r="F44" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G44" s="5">
+      <c r="F44" s="5">
+        <v>1</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H44" s="6">
         <v>2018</v>
       </c>
     </row>
-    <row r="45" spans="1:16">
+    <row r="45" spans="1:17">
       <c r="A45" s="22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C45" s="16">
         <v>0.998</v>
@@ -2742,19 +2878,22 @@
       <c r="E45" s="27">
         <v>0</v>
       </c>
-      <c r="F45" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G45" s="5">
+      <c r="F45" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H45" s="6">
         <v>2018</v>
       </c>
     </row>
-    <row r="46" spans="1:16">
+    <row r="46" spans="1:17">
       <c r="A46" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C46" s="4">
         <v>0.79</v>
@@ -2765,19 +2904,22 @@
       <c r="E46" s="27">
         <v>0.13</v>
       </c>
-      <c r="F46" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G46" s="3">
+      <c r="F46" s="5">
+        <v>1.645</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H46" s="3">
         <v>2019</v>
       </c>
     </row>
-    <row r="47" spans="1:16">
+    <row r="47" spans="1:17">
       <c r="A47" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C47" s="4">
         <v>0.977</v>
@@ -2788,19 +2930,22 @@
       <c r="E47" s="4">
         <v>0.017</v>
       </c>
-      <c r="F47" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="F47" s="5">
+        <v>1</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H47" s="3">
         <v>2019</v>
       </c>
     </row>
-    <row r="48" spans="1:16">
+    <row r="48" spans="1:17">
       <c r="A48" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C48" s="16">
         <v>0.41</v>
@@ -2811,19 +2956,22 @@
       <c r="E48" s="16">
         <v>0.03</v>
       </c>
-      <c r="F48" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G48" s="3">
+      <c r="F48" s="5">
+        <v>1</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H48" s="3">
         <v>2019</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:8">
       <c r="A49" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C49" s="4">
         <v>0.82</v>
@@ -2834,19 +2982,22 @@
       <c r="E49" s="4">
         <v>0.04</v>
       </c>
-      <c r="F49" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G49" s="3">
+      <c r="F49" s="5">
+        <v>1.645</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H49" s="3">
         <v>2019</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:8">
       <c r="A50" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C50" s="4">
         <v>0.97</v>
@@ -2854,22 +3005,25 @@
       <c r="D50" s="4">
         <v>0</v>
       </c>
-      <c r="E50" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="F50" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G50" s="3">
+      <c r="E50" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F50" s="5">
+        <v>1.645</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H50" s="3">
         <v>2019</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:8">
       <c r="A51" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C51" s="4">
         <v>0.8</v>
@@ -2880,19 +3034,22 @@
       <c r="E51" s="4">
         <v>0.02</v>
       </c>
-      <c r="F51" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G51" s="3">
+      <c r="F51" s="5">
+        <v>1.645</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H51" s="3">
         <v>2019</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:8">
       <c r="A52" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C52" s="4">
         <v>0.78</v>
@@ -2903,19 +3060,22 @@
       <c r="E52" s="4">
         <v>0.04</v>
       </c>
-      <c r="F52" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G52" s="3">
+      <c r="F52" s="5">
+        <v>1.645</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H52" s="3">
         <v>2019</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:8">
       <c r="A53" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C53" s="27">
         <v>0.2</v>
@@ -2926,42 +3086,48 @@
       <c r="E53" s="27">
         <v>0</v>
       </c>
-      <c r="F53" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G53" s="3">
+      <c r="F53" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H53" s="3">
         <v>2019</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:8">
       <c r="A54" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C54" s="16">
         <v>0.86</v>
       </c>
-      <c r="D54" s="9" t="s">
-        <v>31</v>
+      <c r="D54" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="E54" s="16">
         <v>0</v>
       </c>
-      <c r="F54" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G54" s="3">
+      <c r="F54" s="5">
+        <v>3.29</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H54" s="3">
         <v>2019</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:8">
       <c r="A55" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C55" s="4">
         <v>0.72</v>
@@ -2969,22 +3135,25 @@
       <c r="D55" s="4">
         <v>0</v>
       </c>
-      <c r="E55" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="F55" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G55" s="3">
+      <c r="E55" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F55" s="5">
+        <v>1.645</v>
+      </c>
+      <c r="G55" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H55" s="3">
         <v>2019</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:8">
       <c r="A56" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C56" s="4">
         <v>0.97</v>
@@ -2995,42 +3164,48 @@
       <c r="E56" s="4">
         <v>0.02</v>
       </c>
-      <c r="F56" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G56" s="3">
+      <c r="F56" s="5">
+        <v>1</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H56" s="3">
         <v>2019</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:8">
       <c r="A57" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C57" s="4">
         <v>0.25</v>
       </c>
-      <c r="D57" s="9" t="s">
-        <v>31</v>
+      <c r="D57" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="E57" s="4">
         <v>0</v>
       </c>
-      <c r="F57" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G57" s="3">
+      <c r="F57" s="5">
+        <v>1.645</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H57" s="3">
         <v>2019</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:8">
       <c r="A58" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C58" s="16">
         <v>0.655</v>
@@ -3041,19 +3216,22 @@
       <c r="E58" s="27">
         <v>0.155</v>
       </c>
-      <c r="F58" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G58" s="3">
+      <c r="F58" s="5">
+        <v>1.645</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H58" s="3">
         <v>2024</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:8">
       <c r="A59" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C59" s="4">
         <v>0.84</v>
@@ -3064,19 +3242,22 @@
       <c r="E59" s="4">
         <v>0.17</v>
       </c>
-      <c r="F59" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="F59" s="5">
+        <v>1.645</v>
+      </c>
+      <c r="G59" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H59" s="3">
         <v>2024</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:8">
       <c r="A60" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C60" s="16">
         <v>0.7</v>
@@ -3087,19 +3268,22 @@
       <c r="E60" s="27">
         <v>0.17</v>
       </c>
-      <c r="F60" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G60" s="3">
+      <c r="F60" s="5">
+        <v>1</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H60" s="3">
         <v>2024</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:8">
       <c r="A61" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C61" s="16">
         <v>0.94</v>
@@ -3110,19 +3294,22 @@
       <c r="E61" s="16">
         <v>0.06</v>
       </c>
-      <c r="F61" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G61" s="3">
+      <c r="F61" s="5">
+        <v>2</v>
+      </c>
+      <c r="G61" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H61" s="3">
         <v>2025</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:8">
       <c r="A62" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C62" s="4">
         <v>0.49</v>
@@ -3133,19 +3320,22 @@
       <c r="E62" s="16">
         <v>0.07</v>
       </c>
-      <c r="F62" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G62" s="3">
+      <c r="F62" s="5">
+        <v>1.645</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H62" s="3">
         <v>2025</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:8">
       <c r="A63" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C63" s="16">
         <v>0.665</v>
@@ -3156,10 +3346,13 @@
       <c r="E63" s="27">
         <v>0.035</v>
       </c>
-      <c r="F63" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G63" s="3">
+      <c r="F63" s="5">
+        <v>1</v>
+      </c>
+      <c r="G63" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H63" s="3">
         <v>2025</v>
       </c>
     </row>

--- a/data/数据收集 表3 蒙特卡洛模拟用.xlsx
+++ b/data/数据收集 表3 蒙特卡洛模拟用.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="9105" windowHeight="6487"/>
+    <workbookView windowWidth="18052" windowHeight="8655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -238,6 +238,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -262,13 +269,6 @@
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
@@ -871,7 +871,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -881,25 +881,28 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -917,16 +920,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -936,6 +936,15 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1469,367 +1478,367 @@
   <dimension ref="A1:R39"/>
   <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="15.75"/>
   <cols>
-    <col min="2" max="2" width="29.5840707964602" style="3" customWidth="1"/>
-    <col min="3" max="3" width="19.5221238938053" style="3" customWidth="1"/>
-    <col min="4" max="4" width="8.96460176991151" style="4" customWidth="1"/>
-    <col min="5" max="6" width="11.2212389380531" style="4" customWidth="1"/>
-    <col min="7" max="7" width="38.5132743362832" style="5" customWidth="1"/>
-    <col min="8" max="8" width="38.5132743362832" style="6" customWidth="1"/>
-    <col min="9" max="9" width="24.2920353982301" style="3" customWidth="1"/>
+    <col min="2" max="2" width="29.5840707964602" style="4" customWidth="1"/>
+    <col min="3" max="3" width="19.5221238938053" style="4" customWidth="1"/>
+    <col min="4" max="4" width="8.96460176991151" style="5" customWidth="1"/>
+    <col min="5" max="6" width="11.2212389380531" style="5" customWidth="1"/>
+    <col min="7" max="7" width="38.5132743362832" style="6" customWidth="1"/>
+    <col min="8" max="8" width="38.5132743362832" style="7" customWidth="1"/>
+    <col min="9" max="9" width="24.2920353982301" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:18">
-      <c r="A2" s="9">
+      <c r="A2" s="10">
         <v>1</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="12">
         <v>0.817</v>
       </c>
-      <c r="E2" s="11">
+      <c r="E2" s="12">
         <v>0.014</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="12">
         <v>0.014</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="6">
         <v>1.645</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="7">
         <v>2020</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:18">
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="12">
         <v>0.99</v>
       </c>
-      <c r="E3" s="11">
+      <c r="E3" s="12">
         <v>0.003</v>
       </c>
-      <c r="F3" s="11">
+      <c r="F3" s="12">
         <v>0.003</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="6">
         <v>1</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I3" s="7">
         <v>2013</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:18">
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="13">
         <v>0.85</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="12">
         <v>0.07</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="12">
         <v>0.07</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="6">
         <v>1.645</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:18">
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="13">
         <v>0.92</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="12">
         <v>0.04</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="12">
         <v>0.04</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="6">
         <v>3</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="7">
         <v>2016</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:18">
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="13">
         <v>0.985</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="12">
         <v>0.014</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="12">
         <v>0.005</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="6">
         <v>1</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="7">
         <v>2013</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:18">
-      <c r="A7" s="9">
+      <c r="A7" s="10">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="12">
         <v>0.902</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="12">
         <v>0.053</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="12">
         <v>0.054</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="6">
         <v>1.645</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="7">
         <v>2021</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:18">
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="12">
         <v>0.959</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="13">
         <v>0.039</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="13">
         <v>0.031</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="6">
         <v>1</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="H8" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="7">
         <v>2017</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" spans="1:18">
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="13">
         <v>0.65</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="13">
         <v>0.24</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="13">
         <v>0.14</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="6">
         <v>1</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="H9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="7">
         <v>2021</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" spans="1:18">
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="13">
         <v>0.98</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="13">
         <v>0.02</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="13">
         <v>0.01</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="6">
         <v>1</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="H10" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="7">
         <v>2021</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:18">
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="12">
         <v>0.46</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="13">
         <v>0.12</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="13">
         <v>0.12</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11" s="6">
         <v>1</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="H11" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I11" s="6">
+      <c r="I11" s="7">
         <v>2021</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:18">
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="12">
         <v>0.67</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="13">
         <v>0.08</v>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="13">
         <v>0.15</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="6">
         <v>1.645</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="H12" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="I12" s="6">
+      <c r="I12" s="7">
         <v>2002</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:18">
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="12">
         <v>0.8</v>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="12">
         <v>0.05</v>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="12">
         <v>0.05</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="6">
         <v>1</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="H13" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="6">
+      <c r="I13" s="7">
         <v>2002</v>
       </c>
     </row>
     <row r="14" spans="1:18">
-      <c r="A14" s="16">
+      <c r="A14" s="10">
         <v>3</v>
       </c>
       <c r="B14" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="4" t="s">
         <v>21</v>
       </c>
       <c r="D14" s="18">
@@ -1841,10 +1850,10 @@
       <c r="F14" s="18">
         <v>0.01</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G14" s="6">
         <v>1</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="H14" s="7" t="s">
         <v>10</v>
       </c>
       <c r="I14" s="19" t="s">
@@ -1858,7 +1867,7 @@
       <c r="B15" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="4" t="s">
         <v>27</v>
       </c>
       <c r="D15" s="18">
@@ -1870,10 +1879,10 @@
       <c r="F15" s="18">
         <v>0.3</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G15" s="6">
         <v>1</v>
       </c>
-      <c r="H15" s="6" t="s">
+      <c r="H15" s="7" t="s">
         <v>15</v>
       </c>
       <c r="I15" s="20">
@@ -1884,13 +1893,13 @@
       <c r="L15" s="20"/>
     </row>
     <row r="16" spans="1:18">
-      <c r="A16" s="16">
+      <c r="A16" s="10">
         <v>4</v>
       </c>
       <c r="B16" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="4" t="s">
         <v>29</v>
       </c>
       <c r="D16" s="18">
@@ -1902,10 +1911,10 @@
       <c r="F16" s="18">
         <v>0.014</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G16" s="6">
         <v>2.576</v>
       </c>
-      <c r="H16" s="6" t="s">
+      <c r="H16" s="7" t="s">
         <v>15</v>
       </c>
       <c r="I16" s="20" t="s">
@@ -1925,7 +1934,7 @@
       <c r="B17" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="4" t="s">
         <v>31</v>
       </c>
       <c r="D17" s="18">
@@ -1937,10 +1946,10 @@
       <c r="F17" s="18">
         <v>0.01</v>
       </c>
-      <c r="G17" s="5">
+      <c r="G17" s="6">
         <v>1</v>
       </c>
-      <c r="H17" s="6" t="s">
+      <c r="H17" s="7" t="s">
         <v>10</v>
       </c>
       <c r="I17" s="20">
@@ -1972,10 +1981,10 @@
       <c r="F18" s="18">
         <v>0.01</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G18" s="6">
         <v>1</v>
       </c>
-      <c r="H18" s="6" t="s">
+      <c r="H18" s="7" t="s">
         <v>10</v>
       </c>
       <c r="I18" s="20">
@@ -1995,7 +2004,7 @@
       <c r="B19" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="4" t="s">
         <v>33</v>
       </c>
       <c r="D19" s="18">
@@ -2007,10 +2016,10 @@
       <c r="F19" s="18">
         <v>0.009</v>
       </c>
-      <c r="G19" s="5">
+      <c r="G19" s="6">
         <v>1.645</v>
       </c>
-      <c r="H19" s="6" t="s">
+      <c r="H19" s="7" t="s">
         <v>15</v>
       </c>
       <c r="I19" s="20" t="s">
@@ -2027,16 +2036,16 @@
       <c r="R19" s="20"/>
     </row>
     <row r="20" spans="1:18">
-      <c r="A20" s="16">
+      <c r="A20" s="10">
         <v>5</v>
       </c>
       <c r="B20" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="5">
         <v>0.76</v>
       </c>
       <c r="E20" s="18">
@@ -2045,13 +2054,13 @@
       <c r="F20" s="18">
         <v>0.01</v>
       </c>
-      <c r="G20" s="5">
+      <c r="G20" s="6">
         <v>1</v>
       </c>
-      <c r="H20" s="6" t="s">
+      <c r="H20" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I20" s="4">
         <v>1998</v>
       </c>
     </row>
@@ -2059,7 +2068,7 @@
       <c r="B21" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D21" s="18">
@@ -2071,94 +2080,94 @@
       <c r="F21" s="18">
         <v>0.15</v>
       </c>
-      <c r="G21" s="5">
+      <c r="G21" s="6">
         <v>1.645</v>
       </c>
-      <c r="H21" s="6" t="s">
+      <c r="H21" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="I21" s="4" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:18">
-      <c r="A22" s="16">
+      <c r="A22" s="10">
         <v>6</v>
       </c>
       <c r="B22" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="4" t="s">
         <v>40</v>
       </c>
       <c r="D22" s="18">
         <v>0.94</v>
       </c>
-      <c r="E22" s="11">
+      <c r="E22" s="12">
         <v>0.01</v>
       </c>
-      <c r="F22" s="11">
+      <c r="F22" s="12">
         <v>0.01</v>
       </c>
-      <c r="G22" s="5">
+      <c r="G22" s="6">
         <v>1.645</v>
       </c>
-      <c r="H22" s="6" t="s">
+      <c r="H22" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="6">
+      <c r="I22" s="7">
         <v>2018</v>
       </c>
     </row>
-    <row r="23" spans="1:18">
-      <c r="B23" s="17" t="s">
+    <row r="23" s="3" customFormat="1" spans="1:18">
+      <c r="B23" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D23" s="18">
+      <c r="D23" s="23">
         <v>-0.396</v>
       </c>
-      <c r="E23" s="18">
+      <c r="E23" s="23">
         <v>0.432</v>
       </c>
-      <c r="F23" s="18">
+      <c r="F23" s="23">
         <v>0.661</v>
       </c>
-      <c r="G23" s="5">
+      <c r="G23" s="24">
         <v>1</v>
       </c>
-      <c r="H23" s="6" t="s">
+      <c r="H23" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="I23" s="6" t="s">
+      <c r="I23" s="8" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:18">
-      <c r="B24" s="17" t="s">
+    <row r="24" s="3" customFormat="1" spans="1:18">
+      <c r="B24" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="24">
         <v>-0.141</v>
       </c>
-      <c r="E24" s="18">
+      <c r="E24" s="23">
         <v>0.564</v>
       </c>
-      <c r="F24" s="18">
+      <c r="F24" s="23">
         <v>0.492</v>
       </c>
-      <c r="G24" s="5">
+      <c r="G24" s="24">
         <v>1</v>
       </c>
-      <c r="H24" s="6" t="s">
+      <c r="H24" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="I24" s="6" t="s">
+      <c r="I24" s="8" t="s">
         <v>42</v>
       </c>
     </row>
@@ -2166,25 +2175,25 @@
       <c r="B25" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="5">
         <v>0.77</v>
       </c>
-      <c r="E25" s="11">
+      <c r="E25" s="12">
         <v>0.21</v>
       </c>
-      <c r="F25" s="11">
+      <c r="F25" s="12">
         <v>0.21</v>
       </c>
-      <c r="G25" s="5">
+      <c r="G25" s="6">
         <v>1.645</v>
       </c>
-      <c r="H25" s="6" t="s">
+      <c r="H25" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I25" s="6">
+      <c r="I25" s="7">
         <v>2018</v>
       </c>
     </row>
@@ -2192,10 +2201,10 @@
       <c r="B26" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="5">
         <v>0.988</v>
       </c>
       <c r="E26" s="18">
@@ -2204,13 +2213,13 @@
       <c r="F26" s="18">
         <v>0.006</v>
       </c>
-      <c r="G26" s="5">
+      <c r="G26" s="6">
         <v>1</v>
       </c>
-      <c r="H26" s="6" t="s">
+      <c r="H26" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="I26" s="6" t="s">
+      <c r="I26" s="7" t="s">
         <v>42</v>
       </c>
     </row>
@@ -2218,7 +2227,7 @@
       <c r="B27" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="4" t="s">
         <v>45</v>
       </c>
       <c r="D27" s="18">
@@ -2230,13 +2239,13 @@
       <c r="F27" s="18">
         <v>0.09</v>
       </c>
-      <c r="G27" s="5">
+      <c r="G27" s="6">
         <v>1</v>
       </c>
-      <c r="H27" s="6" t="s">
+      <c r="H27" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I27" s="6">
+      <c r="I27" s="7">
         <v>2018</v>
       </c>
     </row>
@@ -2244,10 +2253,10 @@
       <c r="B28" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28" s="5">
         <v>0.2</v>
       </c>
       <c r="E28" s="18">
@@ -2256,50 +2265,50 @@
       <c r="F28" s="18">
         <v>0.2</v>
       </c>
-      <c r="G28" s="5">
+      <c r="G28" s="6">
         <v>1</v>
       </c>
-      <c r="H28" s="6" t="s">
+      <c r="H28" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I28" s="6">
+      <c r="I28" s="7">
         <v>2018</v>
       </c>
     </row>
     <row r="29" spans="1:18">
-      <c r="A29" s="16">
+      <c r="A29" s="10">
         <v>7</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29" s="5">
         <v>0.977</v>
       </c>
-      <c r="E29" s="4">
+      <c r="E29" s="5">
         <v>0.015</v>
       </c>
-      <c r="F29" s="4">
+      <c r="F29" s="5">
         <v>0.017</v>
       </c>
-      <c r="G29" s="5">
+      <c r="G29" s="6">
         <v>1</v>
       </c>
-      <c r="H29" s="6" t="s">
+      <c r="H29" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="I29" s="3">
+      <c r="I29" s="4">
         <v>2019</v>
       </c>
     </row>
     <row r="30" spans="1:18">
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="4" t="s">
         <v>48</v>
       </c>
       <c r="D30" s="18">
@@ -2311,183 +2320,183 @@
       <c r="F30" s="18">
         <v>0.03</v>
       </c>
-      <c r="G30" s="5">
+      <c r="G30" s="6">
         <v>1</v>
       </c>
-      <c r="H30" s="6" t="s">
+      <c r="H30" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I30" s="3">
+      <c r="I30" s="4">
         <v>2019</v>
       </c>
     </row>
     <row r="31" spans="1:18">
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D31" s="5">
         <v>0.82</v>
       </c>
-      <c r="E31" s="4">
+      <c r="E31" s="5">
         <v>0.03</v>
       </c>
-      <c r="F31" s="4">
+      <c r="F31" s="5">
         <v>0.04</v>
       </c>
-      <c r="G31" s="5">
+      <c r="G31" s="6">
         <v>1.645</v>
       </c>
-      <c r="H31" s="6" t="s">
+      <c r="H31" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="I31" s="3">
+      <c r="I31" s="4">
         <v>2019</v>
       </c>
     </row>
     <row r="32" spans="1:18">
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D32" s="5">
         <v>0.8</v>
       </c>
-      <c r="E32" s="4">
+      <c r="E32" s="5">
         <v>0.02</v>
       </c>
-      <c r="F32" s="4">
+      <c r="F32" s="5">
         <v>0.02</v>
       </c>
-      <c r="G32" s="5">
+      <c r="G32" s="6">
         <v>1.645</v>
       </c>
-      <c r="H32" s="6" t="s">
+      <c r="H32" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I32" s="3">
+      <c r="I32" s="4">
         <v>2019</v>
       </c>
     </row>
     <row r="33" spans="1:9">
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D33" s="4">
+      <c r="D33" s="5">
         <v>0.78</v>
       </c>
-      <c r="E33" s="4">
+      <c r="E33" s="5">
         <v>0.04</v>
       </c>
-      <c r="F33" s="4">
+      <c r="F33" s="5">
         <v>0.04</v>
       </c>
-      <c r="G33" s="5">
+      <c r="G33" s="6">
         <v>1.645</v>
       </c>
-      <c r="H33" s="6" t="s">
+      <c r="H33" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="I33" s="3">
+      <c r="I33" s="4">
         <v>2019</v>
       </c>
     </row>
     <row r="34" spans="1:9">
-      <c r="A34" s="16">
+      <c r="A34" s="10">
         <v>8</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="4" t="s">
         <v>53</v>
       </c>
       <c r="D34" s="18">
         <v>0.655</v>
       </c>
-      <c r="E34" s="22">
+      <c r="E34" s="25">
         <v>0.155</v>
       </c>
-      <c r="F34" s="22">
+      <c r="F34" s="25">
         <v>0.155</v>
       </c>
-      <c r="G34" s="5">
+      <c r="G34" s="6">
         <v>1.645</v>
       </c>
-      <c r="H34" s="6" t="s">
+      <c r="H34" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="I34" s="3">
+      <c r="I34" s="4">
         <v>2024</v>
       </c>
     </row>
     <row r="35" spans="1:9">
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D35" s="4">
+      <c r="D35" s="5">
         <v>0.84</v>
       </c>
-      <c r="E35" s="4">
+      <c r="E35" s="5">
         <v>0.26</v>
       </c>
-      <c r="F35" s="4">
+      <c r="F35" s="5">
         <v>0.17</v>
       </c>
-      <c r="G35" s="5">
+      <c r="G35" s="6">
         <v>1.645</v>
       </c>
-      <c r="H35" s="6" t="s">
+      <c r="H35" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="I35" s="3">
+      <c r="I35" s="4">
         <v>2024</v>
       </c>
     </row>
     <row r="36" spans="1:9">
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="4" t="s">
         <v>55</v>
       </c>
       <c r="D36" s="18">
         <v>0.7</v>
       </c>
-      <c r="E36" s="22">
+      <c r="E36" s="25">
         <v>0.17</v>
       </c>
-      <c r="F36" s="22">
+      <c r="F36" s="25">
         <v>0.17</v>
       </c>
-      <c r="G36" s="5">
+      <c r="G36" s="6">
         <v>1</v>
       </c>
-      <c r="H36" s="6" t="s">
+      <c r="H36" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I36" s="3">
+      <c r="I36" s="4">
         <v>2024</v>
       </c>
     </row>
     <row r="37" spans="1:9">
-      <c r="A37" s="16">
+      <c r="A37" s="10">
         <v>9</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="4" t="s">
         <v>57</v>
       </c>
       <c r="D37" s="18">
@@ -2499,24 +2508,24 @@
       <c r="F37" s="18">
         <v>0.06</v>
       </c>
-      <c r="G37" s="5">
+      <c r="G37" s="6">
         <v>2</v>
       </c>
-      <c r="H37" s="6" t="s">
+      <c r="H37" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="I37" s="3">
+      <c r="I37" s="4">
         <v>2025</v>
       </c>
     </row>
     <row r="38" spans="1:9">
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D38" s="4">
+      <c r="D38" s="5">
         <v>0.49</v>
       </c>
       <c r="E38" s="18">
@@ -2525,39 +2534,39 @@
       <c r="F38" s="18">
         <v>0.07</v>
       </c>
-      <c r="G38" s="5">
+      <c r="G38" s="6">
         <v>1.645</v>
       </c>
-      <c r="H38" s="6" t="s">
+      <c r="H38" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I38" s="3">
+      <c r="I38" s="4">
         <v>2025</v>
       </c>
     </row>
     <row r="39" spans="1:9">
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="4" t="s">
         <v>53</v>
       </c>
       <c r="D39" s="18">
         <v>0.665</v>
       </c>
-      <c r="E39" s="22">
+      <c r="E39" s="25">
         <v>0.035</v>
       </c>
-      <c r="F39" s="22">
+      <c r="F39" s="25">
         <v>0.035</v>
       </c>
-      <c r="G39" s="5">
+      <c r="G39" s="6">
         <v>1</v>
       </c>
-      <c r="H39" s="6" t="s">
+      <c r="H39" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I39" s="3">
+      <c r="I39" s="4">
         <v>2025</v>
       </c>
     </row>

--- a/data/数据收集 表3 蒙特卡洛模拟用.xlsx
+++ b/data/数据收集 表3 蒙特卡洛模拟用.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="57">
   <si>
     <t>源</t>
   </si>
@@ -152,16 +152,10 @@
     <t>Fan 2024</t>
   </si>
   <si>
-    <t>Dias 2024-1</t>
+    <t>Banerjee 2024</t>
   </si>
   <si>
     <t>2018-2019 </t>
-  </si>
-  <si>
-    <t>Dias 2024-2</t>
-  </si>
-  <si>
-    <t>Banerjee 2024</t>
   </si>
   <si>
     <t>Zhao 2021</t>
@@ -238,37 +232,37 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
@@ -871,7 +865,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -881,28 +875,25 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -920,13 +911,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -936,15 +927,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1475,1098 +1457,1046 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R39"/>
+  <dimension ref="A1:R37"/>
   <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="15.75"/>
   <cols>
-    <col min="2" max="2" width="29.5840707964602" style="4" customWidth="1"/>
-    <col min="3" max="3" width="19.5221238938053" style="4" customWidth="1"/>
-    <col min="4" max="4" width="8.96460176991151" style="5" customWidth="1"/>
-    <col min="5" max="6" width="11.2212389380531" style="5" customWidth="1"/>
-    <col min="7" max="7" width="38.5132743362832" style="6" customWidth="1"/>
-    <col min="8" max="8" width="38.5132743362832" style="7" customWidth="1"/>
-    <col min="9" max="9" width="24.2920353982301" style="4" customWidth="1"/>
+    <col min="2" max="2" width="29.5840707964602" style="3" customWidth="1"/>
+    <col min="3" max="3" width="19.5221238938053" style="3" customWidth="1"/>
+    <col min="4" max="4" width="8.96460176991151" style="4" customWidth="1"/>
+    <col min="5" max="6" width="11.2212389380531" style="4" customWidth="1"/>
+    <col min="7" max="7" width="38.5132743362832" style="5" customWidth="1"/>
+    <col min="8" max="8" width="38.5132743362832" style="6" customWidth="1"/>
+    <col min="9" max="9" width="24.2920353982301" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:18">
-      <c r="A2" s="10">
+      <c r="A2" s="9">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="12">
+      <c r="D2" s="11">
         <v>0.817</v>
       </c>
-      <c r="E2" s="12">
+      <c r="E2" s="11">
         <v>0.014</v>
       </c>
-      <c r="F2" s="12">
+      <c r="F2" s="11">
         <v>0.014</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="5">
         <v>1.645</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="6">
         <v>2020</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:18">
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="11">
         <v>0.99</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="11">
         <v>0.003</v>
       </c>
-      <c r="F3" s="12">
+      <c r="F3" s="11">
         <v>0.003</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="5">
         <v>1</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="7">
+      <c r="I3" s="6">
         <v>2013</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:18">
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="12">
         <v>0.85</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="11">
         <v>0.07</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="11">
         <v>0.07</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="5">
         <v>1.645</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:18">
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="12">
         <v>0.92</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="11">
         <v>0.04</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="11">
         <v>0.04</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="5">
         <v>3</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="6">
         <v>2016</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:18">
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="12">
         <v>0.985</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="11">
         <v>0.014</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="11">
         <v>0.005</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="5">
         <v>1</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="6">
         <v>2013</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:18">
-      <c r="A7" s="10">
+      <c r="A7" s="9">
         <v>2</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="11">
         <v>0.902</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="11">
         <v>0.053</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="11">
         <v>0.054</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="5">
         <v>1.645</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="6">
         <v>2021</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:18">
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="11">
         <v>0.959</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="12">
         <v>0.039</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="12">
         <v>0.031</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="5">
         <v>1</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I8" s="7">
+      <c r="I8" s="6">
         <v>2017</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" spans="1:18">
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="12">
         <v>0.65</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="12">
         <v>0.24</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="12">
         <v>0.14</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="5">
         <v>1</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I9" s="7">
+      <c r="I9" s="6">
         <v>2021</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" spans="1:18">
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="12">
         <v>0.98</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="12">
         <v>0.02</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="12">
         <v>0.01</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="5">
         <v>1</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I10" s="7">
+      <c r="I10" s="6">
         <v>2021</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:18">
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="11">
         <v>0.46</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="12">
         <v>0.12</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="12">
         <v>0.12</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="5">
         <v>1</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I11" s="7">
+      <c r="I11" s="6">
         <v>2021</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:18">
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="11">
         <v>0.67</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="12">
         <v>0.08</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="12">
         <v>0.15</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="5">
         <v>1.645</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I12" s="7">
+      <c r="I12" s="6">
         <v>2002</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:18">
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="11">
         <v>0.8</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="11">
         <v>0.05</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="11">
         <v>0.05</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="5">
         <v>1</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="H13" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="7">
+      <c r="I13" s="6">
         <v>2002</v>
       </c>
     </row>
     <row r="14" spans="1:18">
-      <c r="A14" s="10">
+      <c r="A14" s="9">
         <v>3</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="18">
+      <c r="D14" s="17">
         <v>0.98</v>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="17">
         <v>0.02</v>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="17">
         <v>0.01</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="5">
         <v>1</v>
       </c>
-      <c r="H14" s="7" t="s">
+      <c r="H14" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I14" s="19" t="s">
+      <c r="I14" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="J14" s="20"/>
-      <c r="K14" s="20"/>
-      <c r="L14" s="20"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
     </row>
     <row r="15" spans="1:18">
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="18">
+      <c r="D15" s="17">
         <v>0.2</v>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="17">
         <v>0.3</v>
       </c>
-      <c r="F15" s="18">
+      <c r="F15" s="17">
         <v>0.3</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="5">
         <v>1</v>
       </c>
-      <c r="H15" s="7" t="s">
+      <c r="H15" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I15" s="20">
+      <c r="I15" s="19">
         <v>2003</v>
       </c>
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="19"/>
     </row>
     <row r="16" spans="1:18">
-      <c r="A16" s="10">
+      <c r="A16" s="9">
         <v>4</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D16" s="18">
+      <c r="D16" s="17">
         <v>0.863</v>
       </c>
-      <c r="E16" s="18">
+      <c r="E16" s="17">
         <v>0.015</v>
       </c>
-      <c r="F16" s="18">
+      <c r="F16" s="17">
         <v>0.014</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G16" s="5">
         <v>2.576</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="H16" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I16" s="20" t="s">
+      <c r="I16" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-      <c r="M16" s="20"/>
-      <c r="N16" s="20"/>
-      <c r="O16" s="20"/>
-      <c r="P16" s="20"/>
-      <c r="Q16" s="20"/>
-      <c r="R16" s="20"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="19"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="19"/>
+      <c r="O16" s="19"/>
+      <c r="P16" s="19"/>
+      <c r="Q16" s="19"/>
+      <c r="R16" s="19"/>
     </row>
     <row r="17" spans="1:18">
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="18">
+      <c r="D17" s="17">
         <v>0.98</v>
       </c>
-      <c r="E17" s="18">
+      <c r="E17" s="17">
         <v>0.01</v>
       </c>
-      <c r="F17" s="18">
+      <c r="F17" s="17">
         <v>0.01</v>
       </c>
-      <c r="G17" s="6">
+      <c r="G17" s="5">
         <v>1</v>
       </c>
-      <c r="H17" s="7" t="s">
+      <c r="H17" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I17" s="20">
+      <c r="I17" s="19">
         <v>2012</v>
       </c>
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-      <c r="M17" s="20"/>
-      <c r="N17" s="20"/>
-      <c r="O17" s="20"/>
-      <c r="P17" s="20"/>
-      <c r="Q17" s="20"/>
-      <c r="R17" s="20"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="19"/>
+      <c r="M17" s="19"/>
+      <c r="N17" s="19"/>
+      <c r="O17" s="19"/>
+      <c r="P17" s="19"/>
+      <c r="Q17" s="19"/>
+      <c r="R17" s="19"/>
     </row>
     <row r="18" spans="1:18">
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="20" t="s">
+      <c r="C18" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="21">
+      <c r="D18" s="20">
         <v>0.98</v>
       </c>
-      <c r="E18" s="18">
+      <c r="E18" s="17">
         <v>0.01</v>
       </c>
-      <c r="F18" s="18">
+      <c r="F18" s="17">
         <v>0.01</v>
       </c>
-      <c r="G18" s="6">
+      <c r="G18" s="5">
         <v>1</v>
       </c>
-      <c r="H18" s="7" t="s">
+      <c r="H18" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I18" s="20">
+      <c r="I18" s="19">
         <v>2007</v>
       </c>
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-      <c r="M18" s="20"/>
-      <c r="N18" s="20"/>
-      <c r="O18" s="20"/>
-      <c r="P18" s="20"/>
-      <c r="Q18" s="20"/>
-      <c r="R18" s="20"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="19"/>
+      <c r="P18" s="19"/>
+      <c r="Q18" s="19"/>
+      <c r="R18" s="19"/>
     </row>
     <row r="19" spans="1:18">
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D19" s="18">
+      <c r="D19" s="17">
         <v>0.72</v>
       </c>
-      <c r="E19" s="18">
+      <c r="E19" s="17">
         <v>0.017</v>
       </c>
-      <c r="F19" s="18">
+      <c r="F19" s="17">
         <v>0.009</v>
       </c>
-      <c r="G19" s="6">
+      <c r="G19" s="5">
         <v>1.645</v>
       </c>
-      <c r="H19" s="7" t="s">
+      <c r="H19" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I19" s="20" t="s">
+      <c r="I19" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-      <c r="M19" s="20"/>
-      <c r="N19" s="20"/>
-      <c r="O19" s="20"/>
-      <c r="P19" s="20"/>
-      <c r="Q19" s="20"/>
-      <c r="R19" s="20"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="19"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="19"/>
+      <c r="N19" s="19"/>
+      <c r="O19" s="19"/>
+      <c r="P19" s="19"/>
+      <c r="Q19" s="19"/>
+      <c r="R19" s="19"/>
     </row>
     <row r="20" spans="1:18">
-      <c r="A20" s="10">
+      <c r="A20" s="9">
         <v>5</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D20" s="4">
         <v>0.76</v>
       </c>
-      <c r="E20" s="18">
+      <c r="E20" s="17">
         <v>0.01</v>
       </c>
-      <c r="F20" s="18">
+      <c r="F20" s="17">
         <v>0.01</v>
       </c>
-      <c r="G20" s="6">
+      <c r="G20" s="5">
         <v>1</v>
       </c>
-      <c r="H20" s="7" t="s">
+      <c r="H20" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I20" s="4">
+      <c r="I20" s="3">
         <v>1998</v>
       </c>
     </row>
     <row r="21" spans="1:18">
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D21" s="18">
+      <c r="D21" s="17">
         <v>0.72</v>
       </c>
-      <c r="E21" s="18">
+      <c r="E21" s="17">
         <v>0.01</v>
       </c>
-      <c r="F21" s="18">
+      <c r="F21" s="17">
         <v>0.15</v>
       </c>
-      <c r="G21" s="6">
+      <c r="G21" s="5">
         <v>1.645</v>
       </c>
-      <c r="H21" s="7" t="s">
+      <c r="H21" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I21" s="4" t="s">
+      <c r="I21" s="3" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:18">
-      <c r="A22" s="10">
+      <c r="A22" s="9">
         <v>6</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D22" s="18">
+      <c r="D22" s="17">
         <v>0.94</v>
       </c>
-      <c r="E22" s="12">
+      <c r="E22" s="11">
         <v>0.01</v>
       </c>
-      <c r="F22" s="12">
+      <c r="F22" s="11">
         <v>0.01</v>
       </c>
-      <c r="G22" s="6">
+      <c r="G22" s="5">
         <v>1.645</v>
       </c>
-      <c r="H22" s="7" t="s">
+      <c r="H22" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="7">
+      <c r="I22" s="6">
         <v>2018</v>
       </c>
     </row>
-    <row r="23" s="3" customFormat="1" spans="1:18">
-      <c r="B23" s="22" t="s">
+    <row r="23" spans="1:18">
+      <c r="B23" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D23" s="23">
-        <v>-0.396</v>
-      </c>
-      <c r="E23" s="23">
-        <v>0.432</v>
-      </c>
-      <c r="F23" s="23">
-        <v>0.661</v>
-      </c>
-      <c r="G23" s="24">
+      <c r="D23" s="4">
+        <v>0.77</v>
+      </c>
+      <c r="E23" s="11">
+        <v>0.21</v>
+      </c>
+      <c r="F23" s="11">
+        <v>0.21</v>
+      </c>
+      <c r="G23" s="5">
+        <v>1.645</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I23" s="6">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
+      <c r="B24" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D24" s="4">
+        <v>0.988</v>
+      </c>
+      <c r="E24" s="17">
+        <v>0.028</v>
+      </c>
+      <c r="F24" s="17">
+        <v>0.006</v>
+      </c>
+      <c r="G24" s="5">
         <v>1</v>
       </c>
-      <c r="H23" s="8" t="s">
+      <c r="H24" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I23" s="8" t="s">
+      <c r="I24" s="6" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="24" s="3" customFormat="1" spans="1:18">
-      <c r="B24" s="22" t="s">
+    <row r="25" spans="1:18">
+      <c r="B25" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C25" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D24" s="24">
-        <v>-0.141</v>
-      </c>
-      <c r="E24" s="23">
-        <v>0.564</v>
-      </c>
-      <c r="F24" s="23">
-        <v>0.492</v>
-      </c>
-      <c r="G24" s="24">
+      <c r="D25" s="17">
+        <v>0.14</v>
+      </c>
+      <c r="E25" s="17">
+        <v>0.09</v>
+      </c>
+      <c r="F25" s="17">
+        <v>0.09</v>
+      </c>
+      <c r="G25" s="5">
         <v>1</v>
       </c>
-      <c r="H24" s="8" t="s">
+      <c r="H25" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I25" s="6">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18">
+      <c r="B26" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="E26" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="F26" s="17">
+        <v>0.2</v>
+      </c>
+      <c r="G26" s="5">
+        <v>1</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I26" s="6">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18">
+      <c r="A27" s="9">
+        <v>7</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" s="4">
+        <v>0.977</v>
+      </c>
+      <c r="E27" s="4">
+        <v>0.015</v>
+      </c>
+      <c r="F27" s="4">
+        <v>0.017</v>
+      </c>
+      <c r="G27" s="5">
+        <v>1</v>
+      </c>
+      <c r="H27" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I24" s="8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18">
-      <c r="B25" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D25" s="5">
-        <v>0.77</v>
-      </c>
-      <c r="E25" s="12">
-        <v>0.21</v>
-      </c>
-      <c r="F25" s="12">
-        <v>0.21</v>
-      </c>
-      <c r="G25" s="6">
+      <c r="I27" s="3">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18">
+      <c r="B28" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D28" s="17">
+        <v>0.41</v>
+      </c>
+      <c r="E28" s="17">
+        <v>0.03</v>
+      </c>
+      <c r="F28" s="17">
+        <v>0.03</v>
+      </c>
+      <c r="G28" s="5">
+        <v>1</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I28" s="3">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18">
+      <c r="B29" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D29" s="4">
+        <v>0.82</v>
+      </c>
+      <c r="E29" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="F29" s="4">
+        <v>0.04</v>
+      </c>
+      <c r="G29" s="5">
         <v>1.645</v>
       </c>
-      <c r="H25" s="7" t="s">
+      <c r="H29" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="I29" s="3">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18">
+      <c r="B30" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D30" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="E30" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="F30" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="G30" s="5">
+        <v>1.645</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I25" s="7">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18">
-      <c r="B26" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D26" s="5">
-        <v>0.988</v>
-      </c>
-      <c r="E26" s="18">
-        <v>0.028</v>
-      </c>
-      <c r="F26" s="18">
-        <v>0.006</v>
-      </c>
-      <c r="G26" s="6">
+      <c r="I30" s="3">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18">
+      <c r="B31" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D31" s="4">
+        <v>0.78</v>
+      </c>
+      <c r="E31" s="4">
+        <v>0.04</v>
+      </c>
+      <c r="F31" s="4">
+        <v>0.04</v>
+      </c>
+      <c r="G31" s="5">
+        <v>1.645</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="I31" s="3">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18">
+      <c r="A32" s="9">
+        <v>8</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D32" s="17">
+        <v>0.655</v>
+      </c>
+      <c r="E32" s="21">
+        <v>0.155</v>
+      </c>
+      <c r="F32" s="21">
+        <v>0.155</v>
+      </c>
+      <c r="G32" s="5">
+        <v>1.645</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="I32" s="3">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="B33" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D33" s="4">
+        <v>0.84</v>
+      </c>
+      <c r="E33" s="4">
+        <v>0.26</v>
+      </c>
+      <c r="F33" s="4">
+        <v>0.17</v>
+      </c>
+      <c r="G33" s="5">
+        <v>1.645</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="I33" s="3">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="B34" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D34" s="17">
+        <v>0.7</v>
+      </c>
+      <c r="E34" s="21">
+        <v>0.17</v>
+      </c>
+      <c r="F34" s="21">
+        <v>0.17</v>
+      </c>
+      <c r="G34" s="5">
         <v>1</v>
       </c>
-      <c r="H26" s="7" t="s">
+      <c r="H34" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I34" s="3">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="9">
+        <v>9</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D35" s="17">
+        <v>0.94</v>
+      </c>
+      <c r="E35" s="17">
+        <v>0.03</v>
+      </c>
+      <c r="F35" s="17">
+        <v>0.06</v>
+      </c>
+      <c r="G35" s="5">
+        <v>2</v>
+      </c>
+      <c r="H35" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I26" s="7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18">
-      <c r="B27" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D27" s="18">
-        <v>0.14</v>
-      </c>
-      <c r="E27" s="18">
-        <v>0.09</v>
-      </c>
-      <c r="F27" s="18">
-        <v>0.09</v>
-      </c>
-      <c r="G27" s="6">
+      <c r="I35" s="3">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="B36" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D36" s="4">
+        <v>0.49</v>
+      </c>
+      <c r="E36" s="17">
+        <v>0.22</v>
+      </c>
+      <c r="F36" s="17">
+        <v>0.07</v>
+      </c>
+      <c r="G36" s="5">
+        <v>1.645</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I36" s="3">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="B37" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D37" s="17">
+        <v>0.665</v>
+      </c>
+      <c r="E37" s="21">
+        <v>0.035</v>
+      </c>
+      <c r="F37" s="21">
+        <v>0.035</v>
+      </c>
+      <c r="G37" s="5">
         <v>1</v>
       </c>
-      <c r="H27" s="7" t="s">
+      <c r="H37" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I27" s="7">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18">
-      <c r="B28" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D28" s="5">
-        <v>0.2</v>
-      </c>
-      <c r="E28" s="18">
-        <v>0.3</v>
-      </c>
-      <c r="F28" s="18">
-        <v>0.2</v>
-      </c>
-      <c r="G28" s="6">
-        <v>1</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I28" s="7">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18">
-      <c r="A29" s="10">
-        <v>7</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D29" s="5">
-        <v>0.977</v>
-      </c>
-      <c r="E29" s="5">
-        <v>0.015</v>
-      </c>
-      <c r="F29" s="5">
-        <v>0.017</v>
-      </c>
-      <c r="G29" s="6">
-        <v>1</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="I29" s="4">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18">
-      <c r="B30" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D30" s="18">
-        <v>0.41</v>
-      </c>
-      <c r="E30" s="18">
-        <v>0.03</v>
-      </c>
-      <c r="F30" s="18">
-        <v>0.03</v>
-      </c>
-      <c r="G30" s="6">
-        <v>1</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I30" s="4">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18">
-      <c r="B31" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D31" s="5">
-        <v>0.82</v>
-      </c>
-      <c r="E31" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="F31" s="5">
-        <v>0.04</v>
-      </c>
-      <c r="G31" s="6">
-        <v>1.645</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="I31" s="4">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18">
-      <c r="B32" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D32" s="5">
-        <v>0.8</v>
-      </c>
-      <c r="E32" s="5">
-        <v>0.02</v>
-      </c>
-      <c r="F32" s="5">
-        <v>0.02</v>
-      </c>
-      <c r="G32" s="6">
-        <v>1.645</v>
-      </c>
-      <c r="H32" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I32" s="4">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9">
-      <c r="B33" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D33" s="5">
-        <v>0.78</v>
-      </c>
-      <c r="E33" s="5">
-        <v>0.04</v>
-      </c>
-      <c r="F33" s="5">
-        <v>0.04</v>
-      </c>
-      <c r="G33" s="6">
-        <v>1.645</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="I33" s="4">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9">
-      <c r="A34" s="10">
-        <v>8</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D34" s="18">
-        <v>0.655</v>
-      </c>
-      <c r="E34" s="25">
-        <v>0.155</v>
-      </c>
-      <c r="F34" s="25">
-        <v>0.155</v>
-      </c>
-      <c r="G34" s="6">
-        <v>1.645</v>
-      </c>
-      <c r="H34" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="I34" s="4">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9">
-      <c r="B35" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D35" s="5">
-        <v>0.84</v>
-      </c>
-      <c r="E35" s="5">
-        <v>0.26</v>
-      </c>
-      <c r="F35" s="5">
-        <v>0.17</v>
-      </c>
-      <c r="G35" s="6">
-        <v>1.645</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="I35" s="4">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9">
-      <c r="B36" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D36" s="18">
-        <v>0.7</v>
-      </c>
-      <c r="E36" s="25">
-        <v>0.17</v>
-      </c>
-      <c r="F36" s="25">
-        <v>0.17</v>
-      </c>
-      <c r="G36" s="6">
-        <v>1</v>
-      </c>
-      <c r="H36" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I36" s="4">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9">
-      <c r="A37" s="10">
-        <v>9</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D37" s="18">
-        <v>0.94</v>
-      </c>
-      <c r="E37" s="18">
-        <v>0.03</v>
-      </c>
-      <c r="F37" s="18">
-        <v>0.06</v>
-      </c>
-      <c r="G37" s="6">
-        <v>2</v>
-      </c>
-      <c r="H37" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="I37" s="4">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9">
-      <c r="B38" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D38" s="5">
-        <v>0.49</v>
-      </c>
-      <c r="E38" s="18">
-        <v>0.22</v>
-      </c>
-      <c r="F38" s="18">
-        <v>0.07</v>
-      </c>
-      <c r="G38" s="6">
-        <v>1.645</v>
-      </c>
-      <c r="H38" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I38" s="4">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9">
-      <c r="B39" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D39" s="18">
-        <v>0.665</v>
-      </c>
-      <c r="E39" s="25">
-        <v>0.035</v>
-      </c>
-      <c r="F39" s="25">
-        <v>0.035</v>
-      </c>
-      <c r="G39" s="6">
-        <v>1</v>
-      </c>
-      <c r="H39" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I39" s="4">
+      <c r="I37" s="3">
         <v>2025</v>
       </c>
     </row>

--- a/data/数据收集 表3 蒙特卡洛模拟用.xlsx
+++ b/data/数据收集 表3 蒙特卡洛模拟用.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18052" windowHeight="8655"/>
+    <workbookView windowWidth="9105" windowHeight="6487"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/data/数据收集 表3 蒙特卡洛模拟用.xlsx
+++ b/data/数据收集 表3 蒙特卡洛模拟用.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="9105" windowHeight="6487"/>
+    <workbookView windowWidth="18052" windowHeight="8655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
